--- a/output/pdf_financials_xlsx/GOCO.xlsx
+++ b/output/pdf_financials_xlsx/GOCO.xlsx
@@ -580,10 +580,10 @@
         <v>0.220158</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.192818</v>
+        <v>1.262255</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.18475</v>
+        <v>0.443893</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>-1.262255</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.18475</v>
+        <v>-0.443893</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.03707</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.014139</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00634</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.822709</v>
+        <v>-2.859779</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.815045</v>
+        <v>-0.829184</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.815045</v>
+        <v>-0.821385</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.806552</v>
+        <v>-2.843622</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.799111</v>
+        <v>-0.81325</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.813717</v>
+        <v>-0.820057</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.003988</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.382947</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.26751</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.003988</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.382947</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.26751</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.372856</v>
+        <v>0.368868</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.7670090000000001</v>
+        <v>0.384062</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.28598</v>
+        <v>0.01847</v>
       </c>
     </row>
     <row r="49">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018486</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
     </row>
     <row r="125">
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018486</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
     </row>
     <row r="126">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -4330,7 +4330,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -5028,7 +5032,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>-0.018486</v>
       </c>
@@ -5869,7 +5877,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5878,10 +5886,10 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-1.262255</v>
+        <v>1.262255</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.443893</v>
+        <v>0.443893</v>
       </c>
     </row>
     <row r="103">
@@ -5902,7 +5910,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6871,7 +6879,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">

--- a/output/pdf_financials_xlsx/GOCO.xlsx
+++ b/output/pdf_financials_xlsx/GOCO.xlsx
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.003739</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.001586</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>1.8e-05</v>
       </c>
     </row>
     <row r="111">
@@ -4051,7 +4051,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4693,7 +4697,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
         <v>0.003739</v>
       </c>
